--- a/SPG_Customer_Intake_Form.xlsx
+++ b/SPG_Customer_Intake_Form.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="8" min="1" max="1"/>
@@ -880,6 +880,121 @@
         </is>
       </c>
       <c r="Y5" s="15" t="inlineStr">
+        <is>
+          <t>Shoyeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>SPG-003</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Shoyeb Ahmmed</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>ahmmad.ef22@gmail.com</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>0415292944</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>House</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>LAKEMBA</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr"/>
+      <c r="I6" s="15" t="inlineStr"/>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>Under $500k</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>Live in</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q6" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R6" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S6" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T6" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U6" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V6" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W6" s="15" t="inlineStr"/>
+      <c r="X6" s="15" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="Y6" s="15" t="inlineStr">
         <is>
           <t>Shoyeb</t>
         </is>
